--- a/data/trans_dic/IP22D5_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP22D5_R_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 18,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,74</t>
+          <t>0,0; 13,55</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1964</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2829</t>
+          <t>0; 2376</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2435</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2785</t>
+          <t>0; 2494</t>
         </is>
       </c>
     </row>
